--- a/business_forms/046_website_improvement_proposal_form--business_forms.xlsx
+++ b/business_forms/046_website_improvement_proposal_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>project_name</t>
+          <t>Project Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,59 +571,59 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>project_description</t>
+          <t>Project Description</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>business_goals</t>
+          <t>project_timeline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>business_goals</t>
+          <t>Project Timeline</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project_timeline</t>
+          <t>project_budget</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>project_timeline</t>
+          <t>Project Budget</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project_budget</t>
+          <t>project_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>project_budget</t>
+          <t>Project Location</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>project_location</t>
+          <t>project_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>project_location</t>
+          <t>Project Status</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>project_status</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +727,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>project_type</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Project Type</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,87 +773,87 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>website_improvement_project</t>
+          <t>submission_notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>website_improvement_project</t>
+          <t>Submission Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>project_urgency</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>Project Urgency</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>project_urgency</t>
+          <t>project_priority</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>project_urgency</t>
+          <t>Project Priority</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>project_priority</t>
+          <t>website_url</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>project_priority</t>
+          <t>Website URL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -870,13 +870,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>project_notes</t>
+          <t>Project Notes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,35 +888,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>website_url</t>
+          <t>project_files</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>website_url</t>
+          <t>Project Files</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>submission_notes</t>
+          <t>project_file_attachment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>submission_notes</t>
+          <t>Project File Attachment</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,156 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>project_files</t>
+          <t>submission_notes_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>project_files</t>
+          <t>Submission Notes 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>project_type</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>project_urgency</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>project_urgency</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>project_priority</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>project_priority</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>project_location</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>project_location</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submission_notes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submission_notes</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>project_notes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>project_notes</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +960,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option3':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option3': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option4':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option4': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option1':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option1': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option2':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option2': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option3':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option3': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option4':_'joe'}</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option4': 'Joe'}</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option1':_'website_development'}</t>
+          <t>website_development</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option1': 'Website Development'}</t>
+          <t>Website Development</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option2':_'website_maintenance'}</t>
+          <t>website_maintenance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option2': 'Website Maintenance'}</t>
+          <t>Website Maintenance</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option3':_'web_design'}</t>
+          <t>web_design</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option3': 'Web Design'}</t>
+          <t>Web Design</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option1':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option1': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option2':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option2': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option3':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option3': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option1':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option1': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option2':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option2': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1403,114 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option3':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option3': 'Low'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>project_urgency_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'option1':_'high'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'option1': 'High'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>project_urgency_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'option2':_'medium'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'option2': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>project_urgency_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'option3':_'low'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'option3': 'Low'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>project_priority_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'option1':_'high'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'option1': 'High'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>project_priority_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'option2':_'medium'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'option2': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>project_priority_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'option3':_'low'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'option3': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
